--- a/public/StudentTemp.xlsx
+++ b/public/StudentTemp.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t xml:space="preserve">PEN / SR No</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t xml:space="preserve">Transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-session-fees</t>
   </si>
 </sst>
 </file>
@@ -134,17 +137,25 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -270,46 +281,49 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.8"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
